--- a/pdf-analyze/data/history/亚马逊汇总表_1月_1779758343875.xlsx
+++ b/pdf-analyze/data/history/亚马逊汇总表_1月_1779758343875.xlsx
@@ -232,6 +232,12 @@
     <t>宝徕泽土耳其</t>
   </si>
   <si>
+    <t>土耳其</t>
+  </si>
+  <si>
+    <t>TRY</t>
+  </si>
+  <si>
     <t>宝徕泽德国</t>
   </si>
   <si>
@@ -296,12 +302,6 @@
   </si>
   <si>
     <t>宜春市小美仁电子商务有限公司</t>
-  </si>
-  <si>
-    <t>土耳其</t>
-  </si>
-  <si>
-    <t>TRY</t>
   </si>
   <si>
     <t>小美仁德国</t>
@@ -1505,10 +1505,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>0</v>
+        <v>-1466933</v>
       </c>
       <c r="L11" s="5">
-        <v>0</v>
+        <v>697</v>
       </c>
       <c r="M11" s="5">
         <f>G11*F11</f>
@@ -2492,13 +2492,13 @@
         <v>70</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="F29" s="4">
-        <v>7.0288</v>
+        <v>0.1631</v>
       </c>
       <c r="G29" s="5">
         <v>10501</v>
@@ -2542,7 +2542,7 @@
         <v>18</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>70</v>
@@ -2598,13 +2598,13 @@
         <v>18</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>31</v>
@@ -2654,13 +2654,13 @@
         <v>18</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>31</v>
@@ -2710,13 +2710,13 @@
         <v>18</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>31</v>
@@ -2766,16 +2766,16 @@
         <v>18</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F34" s="4">
         <v>1.9453</v>
@@ -2822,13 +2822,13 @@
         <v>18</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>31</v>
@@ -2878,16 +2878,16 @@
         <v>18</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F36" s="4">
         <v>0.7617</v>
@@ -2934,7 +2934,7 @@
         <v>18</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>70</v>
@@ -2990,13 +2990,13 @@
         <v>18</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>31</v>
@@ -3046,13 +3046,13 @@
         <v>18</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>31</v>
@@ -3102,16 +3102,16 @@
         <v>18</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="F40" s="4">
         <v>0.1631</v>
@@ -3161,7 +3161,7 @@
         <v>97</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>30</v>
@@ -3217,10 +3217,10 @@
         <v>98</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>31</v>
@@ -3273,10 +3273,10 @@
         <v>99</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>31</v>
@@ -3329,10 +3329,10 @@
         <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>31</v>
@@ -3385,13 +3385,13 @@
         <v>101</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F45" s="4">
         <v>1.9453</v>
@@ -3441,10 +3441,10 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>31</v>
@@ -3497,13 +3497,13 @@
         <v>103</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F47" s="4">
         <v>0.7617</v>
@@ -3553,7 +3553,7 @@
         <v>104</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>36</v>
@@ -3609,10 +3609,10 @@
         <v>105</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>31</v>
@@ -3665,10 +3665,10 @@
         <v>106</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>31</v>
@@ -3892,7 +3892,7 @@
         <v>108</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>31</v>
@@ -4116,7 +4116,7 @@
         <v>115</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>31</v>
@@ -4172,7 +4172,7 @@
         <v>115</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>31</v>
@@ -4228,7 +4228,7 @@
         <v>115</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>31</v>
@@ -4284,7 +4284,7 @@
         <v>115</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>31</v>
@@ -4676,13 +4676,13 @@
         <v>43</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="F68" s="4">
-        <v>7.0288</v>
+        <v>0.1631</v>
       </c>
       <c r="G68" s="5">
         <v>432.94</v>
@@ -4900,7 +4900,7 @@
         <v>43</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>31</v>
@@ -4956,7 +4956,7 @@
         <v>43</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>31</v>
@@ -5012,7 +5012,7 @@
         <v>43</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>31</v>
@@ -5068,10 +5068,10 @@
         <v>43</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F75" s="4">
         <v>1.9453</v>
@@ -5124,10 +5124,10 @@
         <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F76" s="4">
         <v>0.7617</v>
@@ -5236,7 +5236,7 @@
         <v>43</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>31</v>
@@ -5292,7 +5292,7 @@
         <v>43</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>31</v>
@@ -5740,7 +5740,7 @@
         <v>143</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>31</v>
@@ -5796,7 +5796,7 @@
         <v>143</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>31</v>
@@ -5852,7 +5852,7 @@
         <v>143</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>31</v>
@@ -5964,7 +5964,7 @@
         <v>143</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>31</v>
@@ -6020,7 +6020,7 @@
         <v>143</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>31</v>
@@ -6188,7 +6188,7 @@
         <v>153</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>31</v>
@@ -6244,7 +6244,7 @@
         <v>153</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>31</v>
@@ -6300,7 +6300,7 @@
         <v>153</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>31</v>
